--- a/static/data/exports/Retro_UK_AE-BP_2024.xlsx
+++ b/static/data/exports/Retro_UK_AE-BP_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -566,6 +566,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
         <v>52</v>
       </c>
@@ -615,6 +618,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>52</v>
       </c>
@@ -664,6 +670,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
         <v>52</v>
       </c>
@@ -713,6 +722,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
         <v>52</v>
       </c>
@@ -762,6 +774,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>52</v>
       </c>
@@ -811,6 +826,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
         <v>52</v>
       </c>
@@ -860,6 +878,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" t="n">
         <v>52</v>
       </c>
@@ -909,6 +930,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>52</v>
       </c>
@@ -958,6 +982,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="n">
         <v>52</v>
       </c>
@@ -1007,6 +1034,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" t="n">
         <v>52</v>
       </c>
@@ -1056,6 +1086,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" t="n">
         <v>52</v>
       </c>
@@ -1105,6 +1138,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>52</v>
       </c>
@@ -1154,6 +1190,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>52</v>
       </c>
@@ -1203,6 +1242,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
         <v>52</v>
       </c>
@@ -1252,6 +1294,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>52</v>
       </c>
@@ -1301,6 +1346,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>52</v>
       </c>
@@ -1350,6 +1398,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>52</v>
       </c>
@@ -1399,6 +1450,9 @@
           <t>UK</t>
         </is>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="n">
         <v>52</v>
       </c>
@@ -1447,6 +1501,9 @@
         <is>
           <t>UK</t>
         </is>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>52</v>
